--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43663-2025 artfynd.xlsx
+++ b/artfynd/A 43663-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000788</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
